--- a/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>8.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="E2">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="E3">
-        <v>10.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>63</v>
       </c>
       <c r="D4">
-        <v>56.5</v>
+        <v>62.3</v>
       </c>
       <c r="E4">
-        <v>79.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="E5">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>8.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="E6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C7">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C8">
         <v>191</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C3">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>282</v>
       </c>
       <c r="C4">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
       <c r="D3">
-        <v>14</v>
+        <v>15.1</v>
       </c>
       <c r="E3">
-        <v>10.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C4">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D4">
-        <v>60.5</v>
+        <v>62.3</v>
       </c>
       <c r="E4">
-        <v>83.09999999999999</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="E5">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C7">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C8">
         <v>191</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>282</v>
       </c>
       <c r="C4">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>59.2</v>
+        <v>60.2</v>
       </c>
       <c r="D2">
         <v>61</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4">
-        <v>39.8</v>
+        <v>38.8</v>
       </c>
       <c r="D4">
         <v>4</v>

--- a/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>5.7</v>
+        <v>32.7</v>
       </c>
       <c r="E2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>15.1</v>
+        <v>33.6</v>
       </c>
       <c r="E3">
-        <v>8.199999999999999</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D4">
-        <v>62.3</v>
+        <v>25.7</v>
       </c>
       <c r="E4">
-        <v>86.3</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>11.3</v>
+        <v>6.2</v>
       </c>
       <c r="E5">
-        <v>2.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="C7">
-        <v>209</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C8">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C3">
-        <v>53</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>282</v>
       </c>
       <c r="C4">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C2">
-        <v>60.2</v>
+        <v>65</v>
       </c>
       <c r="D2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E2">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -782,10 +782,16 @@
         </is>
       </c>
       <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2.9</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="E3">
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -795,16 +801,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C4">
-        <v>38.8</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
